--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,7 +515,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -1237,7 +1237,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,7 +1313,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,7 +1351,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,7 +1389,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,7 +1427,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,7 +1465,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,7 +1503,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,7 +1541,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,7 +1579,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,7 +1617,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,7 +1655,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,7 +1693,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,7 +1731,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,7 +1769,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,7 +1807,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,7 +1845,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,7 +1883,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -2187,7 +2187,7 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:57</v>
@@ -2339,7 +2339,7 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:34</v>
@@ -3707,7 +3707,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v>5:18</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>
@@ -3669,7 +3669,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:30</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>
@@ -2263,7 +2263,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -2301,7 +2301,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:25</v>
@@ -1959,19 +1959,19 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>
@@ -1997,19 +1997,19 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:13</v>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E204" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,7 +1313,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,7 +1351,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,7 +1389,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,7 +1427,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,7 +1465,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,7 +1503,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,7 +1541,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,7 +1579,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,7 +1617,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,7 +1655,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,7 +1693,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,7 +1731,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,7 +1769,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,7 +1807,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,7 +1845,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,7 +1883,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -2187,7 +2187,7 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:57</v>
@@ -2339,7 +2339,7 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -1237,7 +1237,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Pongo</v>
+        <v>PONGO</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4631,7 +4631,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Pongo - Single</v>
+        <v>PONGO - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
@@ -4649,7 +4649,7 @@
         <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>PONGO - Rvssian</v>
       </c>
     </row>
     <row r="113">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -2263,7 +2263,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -2301,7 +2301,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>aron! - Wonderful Thing (City View)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>aron! - Wonderful Thing (City View) - aron!</v>
       </c>
     </row>
     <row r="74">
@@ -3555,7 +3555,7 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:55</v>
@@ -3593,7 +3593,7 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:52</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SWIM</v>
+        <v>prom queen</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>ARIRANG</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>2:39</v>
+        <v>2:43</v>
       </c>
       <c r="H102" t="str">
-        <v>BTS</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L102" t="str">
-        <v>SWIM - BTS</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>SWIM</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G103" t="str">
-        <v>5:01</v>
+        <v>2:39</v>
       </c>
       <c r="H103" t="str">
-        <v>RAYE</v>
+        <v>BTS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Loving Life Again</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Rethink Some Things</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>Dandelion</v>
       </c>
       <c r="G105" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L105" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TRANKAITO</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>2:42</v>
+        <v>2:45</v>
       </c>
       <c r="H106" t="str">
-        <v>Feid</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Leak It</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Leak It - Single</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G107" t="str">
-        <v>3:03</v>
+        <v>2:42</v>
       </c>
       <c r="H107" t="str">
-        <v>FLO</v>
+        <v>Feid</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L107" t="str">
-        <v>Leak It - FLO</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>LUVAGIRL</v>
+        <v>Leak It</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:40</v>
+        <v>3:03</v>
       </c>
       <c r="H108" t="str">
-        <v>Coco Jones</v>
+        <v>FLO</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L108" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>D33P3R</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>R3SET</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:25</v>
+        <v>2:40</v>
       </c>
       <c r="H109" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L109" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>D33P3R</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G110" t="str">
-        <v>3:01</v>
+        <v>3:25</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L110" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Don't Hate Me</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H111" t="str">
-        <v>Miles Caton</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L111" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PONGO</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>PONGO - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Rvssian</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L112" t="str">
-        <v>PONGO - Rvssian</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>BOTERO</v>
+        <v>PONGO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>BOTERO - Single</v>
+        <v>PONGO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:14</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Maluma</v>
+        <v>Rvssian</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L113" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>PONGO - Rvssian</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Distance</v>
+        <v>BOTERO</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Distance - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Finn Askew</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L114" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L115" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H116" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L116" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2.0</v>
+        <v>Riptides</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ARIRANG</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G117" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>BTS</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L117" t="str">
-        <v>2.0 - BTS</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>6IXER PARTY</v>
+        <v>2.0</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>6WA</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H118" t="str">
-        <v>BigXthaPlug</v>
+        <v>BTS</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L118" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Highest</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Detour</v>
+        <v>6WA</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Samara Cyn</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L119" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Highest</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G120" t="str">
-        <v>2:40</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Coi Leray</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>So What</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:31</v>
+        <v>2:40</v>
       </c>
       <c r="H121" t="str">
-        <v>MUNA</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L121" t="str">
-        <v>So What - MUNA</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>So What</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>4:31</v>
       </c>
       <c r="H122" t="str">
-        <v>Eli</v>
+        <v>MUNA</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Running To Pain</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>So Help Me God</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G123" t="str">
-        <v>4:06</v>
+        <v>3:12</v>
       </c>
       <c r="H123" t="str">
-        <v>Kelsey Lu</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L123" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G124" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H124" t="str">
-        <v>Anitta</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L124" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Big Mama</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:20</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Latto</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L125" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Bird Flu</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Big Mama</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H126" t="str">
-        <v>6LACK</v>
+        <v>Latto</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L126" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Lighter</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G127" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Jelly Roll</v>
+        <v>6LACK</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L127" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Wide Awake</v>
+        <v>Lighter</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:16</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Stussy</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L128" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Lizzo</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L129" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Niall Horan</v>
+        <v>Lizzo</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L130" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>NORMAL</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>ARIRANG</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G131" t="str">
-        <v>3:01</v>
+        <v>2:34</v>
       </c>
       <c r="H131" t="str">
-        <v>BTS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L131" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Die Living</v>
+        <v>NORMAL</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Die Living - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>ILLENIUM</v>
+        <v>BTS</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L132" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heaven On Earth</v>
+        <v>Die Living</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Pentatonix</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L133" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>an apple a day</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>an apple a day - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>5:16</v>
+        <v>2:59</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L134" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>OUT LATE.</v>
+        <v>an apple a day</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:09</v>
+        <v>5:16</v>
       </c>
       <c r="H135" t="str">
-        <v>Loud Luxury</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L135" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Be With You</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>2:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L136" t="str">
-        <v>Be With You - Muse</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>First Red Rays</v>
+        <v>Be With You</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G137" t="str">
-        <v>8:27</v>
+        <v>3:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Neurosis</v>
+        <v>Muse</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L137" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G138" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H138" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L138" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G139" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H139" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L139" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H140" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L140" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H141" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L141" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H142" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L142" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H143" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L143" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H144" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L144" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H145" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L145" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H146" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L146" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L147" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Kid Cudi</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L148" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H149" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L149" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G150" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H150" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L150" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H151" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L151" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H152" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L152" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G153" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H153" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L153" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G154" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H154" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L154" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G155" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H155" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L155" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G156" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H156" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L156" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G157" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H157" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L157" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L158" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L159" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L160" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G161" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H161" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L161" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H162" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L162" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L163" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H164" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L164" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L165" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L166" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L167" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L168" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L169" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H170" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L170" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H171" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L171" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H172" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L172" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H173" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L173" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H174" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L174" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H175" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L175" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L176" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L178" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L179" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L180" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L181" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H182" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L182" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H183" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L183" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G184" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L184" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H185" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L185" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H186" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L186" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L187" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L188" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H189" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L189" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L190" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H191" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L191" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G192" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H192" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L192" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L193" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G194" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L194" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L195" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H196" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L196" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H197" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L197" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H198" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L198" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H199" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L199" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H200" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L200" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L201" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H202" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L202" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-23</v>
@@ -8089,68 +8089,106 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L203" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D205" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G205" t="str">
         <v>5:19</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H205" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K205" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L205" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:25</v>
@@ -1959,19 +1959,19 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>
@@ -1997,19 +1997,19 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:13</v>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:10</v>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E205" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,7 +515,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -1237,7 +1237,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,7 +1313,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,7 +1351,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,7 +1389,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,7 +1427,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,7 +1465,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,7 +1503,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,7 +1541,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,7 +1579,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,7 +1617,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,7 +1655,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,7 +1693,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,7 +1731,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,7 +1769,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,7 +1807,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,7 +1845,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,7 +1883,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -2187,7 +2187,7 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:57</v>
@@ -2339,7 +2339,7 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -3631,7 +3631,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:53</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>
@@ -3479,7 +3479,7 @@
         <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -2301,7 +2301,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>
@@ -3441,7 +3441,7 @@
         <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v>2:31</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -1997,7 +1997,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -2225,7 +2225,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:13</v>
@@ -2263,7 +2263,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -3365,7 +3365,7 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>2:13</v>
@@ -3403,7 +3403,7 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:19</v>
@@ -4821,7 +4821,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You a Tower</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G117" t="str">
         <v>3:17</v>
@@ -6022,13 +6022,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>if i am me, then who are you?</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-24</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>if i am me, then who are you? - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H149" t="str">
-        <v>Kid Cudi</v>
+        <v>PIAO</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/piao/1633160112</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
       </c>
       <c r="L149" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>if i am me, then who are you? - PIAO</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-24</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H150" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L150" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-24</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G151" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H151" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L151" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-24</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H152" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L152" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-24</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G153" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H153" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L153" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-24</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G154" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H154" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L154" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-24</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G155" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L155" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-24</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H156" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L156" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-24</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G157" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H157" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L157" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-24</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H158" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L158" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-24</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H159" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L159" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-24</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H160" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L160" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-24</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H161" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L161" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-24</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G162" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H162" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L162" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-24</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H163" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L163" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-24</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L164" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-24</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H165" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L165" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-24</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L166" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-24</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H167" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L167" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-24</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L168" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-24</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H169" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-24</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H170" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L170" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-24</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H171" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L171" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-24</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H172" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L172" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-24</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H173" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L173" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-24</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G174" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H174" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L174" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-24</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H175" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L175" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-24</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G176" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H176" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L176" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-24</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L177" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-24</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H178" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-24</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H179" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L179" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-24</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H180" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L180" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-24</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L181" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-24</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H182" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L182" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-24</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H183" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L183" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-24</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H184" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L184" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-24</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G185" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H185" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L185" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-24</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G186" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H186" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L186" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-24</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H187" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L187" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-24</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L188" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-24</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H189" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L189" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-24</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H190" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L190" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-24</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H191" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L191" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-24</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H192" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L192" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-24</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G193" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H193" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L193" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-24</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L194" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-24</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G195" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H195" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L195" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-24</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H196" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L196" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-24</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H197" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L197" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-24</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L198" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-24</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H199" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L199" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-24</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H200" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L200" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-24</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H201" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L201" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-24</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H202" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L202" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-24</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H203" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L203" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-24</v>
@@ -8127,68 +8127,106 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H204" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L204" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D205" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
+      <c r="D206" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G205" t="str">
+      <c r="G206" t="str">
         <v>5:19</v>
       </c>
-      <c r="H205" t="str">
+      <c r="H206" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K205" t="str">
+      <c r="K206" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L205" t="str">
+      <c r="L206" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1959,7 +1959,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>
@@ -1275,19 +1275,19 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,19 +1313,19 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,19 +1351,19 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,19 +1389,19 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,19 +1427,19 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,19 +1465,19 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,19 +1503,19 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,19 +1541,19 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,19 +1579,19 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,19 +1617,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,19 +1655,19 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,19 +1693,19 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,19 +1731,19 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,19 +1769,19 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,19 +1807,19 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,19 +1845,19 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,19 +1883,19 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -1921,19 +1921,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:25</v>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:57</v>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E206" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -1959,7 +1959,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>
@@ -1997,7 +1997,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -3289,7 +3289,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:37</v>
@@ -3327,7 +3327,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:52</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>prom queen</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-25</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>prom queen - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G102" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H102" t="str">
-        <v>Amelia Moore</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L102" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="103">
@@ -4692,13 +4692,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BOTERO</v>
+        <v>prom queen</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-25</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BOTERO - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:14</v>
+        <v>2:43</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L114" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Distance</v>
+        <v>BOTERO</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-25</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Distance - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Finn Askew</v>
+        <v>Maluma</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L115" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-25</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L116" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-25</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You A Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H117" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L117" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2.0</v>
+        <v>Riptides</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-25</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ARIRANG</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G118" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H118" t="str">
-        <v>BTS</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L118" t="str">
-        <v>2.0 - BTS</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>6IXER PARTY</v>
+        <v>2.0</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-25</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>6WA</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H119" t="str">
-        <v>BigXthaPlug</v>
+        <v>BTS</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L119" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Highest</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-25</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Detour</v>
+        <v>6WA</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L120" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Highest</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-25</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G121" t="str">
-        <v>2:40</v>
+        <v>2:56</v>
       </c>
       <c r="H121" t="str">
-        <v>Coi Leray</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>So What</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-25</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:31</v>
+        <v>2:40</v>
       </c>
       <c r="H122" t="str">
-        <v>MUNA</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L122" t="str">
-        <v>So What - MUNA</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>So What</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-25</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G123" t="str">
-        <v>3:12</v>
+        <v>4:31</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>MUNA</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Running To Pain</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-25</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>So Help Me God</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G124" t="str">
-        <v>4:06</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Kelsey Lu</v>
+        <v>Eli</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L124" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-25</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-25</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Big Mama</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:20</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Latto</v>
+        <v>Anitta</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L126" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Bird Flu</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-25</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Big Mama</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H127" t="str">
-        <v>6LACK</v>
+        <v>Latto</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L127" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lighter</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-25</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>6LACK</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L128" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Wide Awake</v>
+        <v>Lighter</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-25</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:16</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>Chris Stussy</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L129" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-25</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Lizzo</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L130" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-25</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Niall Horan</v>
+        <v>Lizzo</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L131" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>NORMAL</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-25</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ARIRANG</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:34</v>
       </c>
       <c r="H132" t="str">
-        <v>BTS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L132" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Die Living</v>
+        <v>NORMAL</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-25</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Die Living - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H133" t="str">
-        <v>ILLENIUM</v>
+        <v>BTS</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L133" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heaven On Earth</v>
+        <v>Die Living</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-25</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Pentatonix</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L134" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>an apple a day</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-25</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>an apple a day - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>5:16</v>
+        <v>2:59</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L135" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>OUT LATE.</v>
+        <v>an apple a day</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-25</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:09</v>
+        <v>5:16</v>
       </c>
       <c r="H136" t="str">
-        <v>Loud Luxury</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L136" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Be With You</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-25</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Wow! Signal</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>2:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Muse</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L137" t="str">
-        <v>Be With You - Muse</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>First Red Rays</v>
+        <v>Be With You</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-25</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G138" t="str">
-        <v>8:27</v>
+        <v>3:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Neurosis</v>
+        <v>Muse</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L138" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-25</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G139" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H139" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L139" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-25</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G140" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H140" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L140" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-25</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L141" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-25</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H142" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L142" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-25</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H143" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L143" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-25</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G144" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H144" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L144" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-25</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L145" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-25</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H146" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L146" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-25</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H147" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L147" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-25</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G148" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H148" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L148" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>if i am me, then who are you?</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-25</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>if i am me, then who are you? - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G149" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H149" t="str">
-        <v>PIAO</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/piao/1633160112</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L149" t="str">
-        <v>if i am me, then who are you? - PIAO</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>if i am me, then who are you?</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-25</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>if i am me, then who are you? - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H150" t="str">
-        <v>Kid Cudi</v>
+        <v>PIAO</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/piao/1633160112</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
       </c>
       <c r="L150" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>if i am me, then who are you? - PIAO</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-25</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H151" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L151" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-25</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G152" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H152" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L152" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-25</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H153" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L153" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-25</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G154" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H154" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L154" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-25</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G155" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H155" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L155" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-25</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G156" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H156" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L156" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-25</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G157" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L157" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-25</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G158" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H158" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L158" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-25</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G159" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H159" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L159" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-25</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G160" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H160" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L160" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-25</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H161" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L161" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-25</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H162" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L162" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-25</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G163" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H163" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L163" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-25</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H164" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L164" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-25</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H165" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L165" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-25</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H166" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L166" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-25</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G167" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H167" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L167" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-25</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L168" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-25</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L169" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-25</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G170" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H170" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L170" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-25</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G171" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H171" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L171" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-25</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G172" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H172" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L172" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-25</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L173" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-25</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H174" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L174" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-25</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G175" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H175" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L175" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-25</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L176" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-25</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H177" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L177" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-25</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L178" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-25</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H179" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L179" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-25</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H180" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L180" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-25</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G181" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H181" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L181" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-25</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H182" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L182" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-25</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L183" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-25</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H184" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L184" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-25</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H185" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L185" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-25</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G186" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H186" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L186" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-25</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G187" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L187" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-25</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H188" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L188" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-25</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L189" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-25</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H190" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L190" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-25</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L191" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-25</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H192" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L192" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-25</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H193" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L193" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-25</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G194" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H194" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L194" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-25</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H195" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L195" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-25</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G196" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H196" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L196" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-25</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H197" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L197" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-25</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H198" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L198" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-25</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H199" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L199" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-25</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H200" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L200" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-25</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H201" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L201" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-25</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H202" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L202" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-25</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H203" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L203" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-25</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H204" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L204" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-25</v>
@@ -8165,68 +8165,106 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H205" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L205" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D206" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
+      <c r="D207" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G206" t="str">
+      <c r="G207" t="str">
         <v>5:19</v>
       </c>
-      <c r="H206" t="str">
+      <c r="H207" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K206" t="str">
+      <c r="K207" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L206" t="str">
+      <c r="L207" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>
@@ -1275,19 +1275,19 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,19 +1313,19 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,19 +1351,19 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,19 +1389,19 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,19 +1427,19 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,19 +1465,19 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,19 +1503,19 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,19 +1541,19 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,19 +1579,19 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,19 +1617,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,19 +1655,19 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,19 +1693,19 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,19 +1731,19 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,19 +1769,19 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,19 +1807,19 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,19 +1845,19 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,19 +1883,19 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -1921,19 +1921,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:25</v>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -8235,7 +8235,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E207" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>
@@ -3251,7 +3251,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v>2:44</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Tractor Beam</v>
+        <v>Automatic</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-26</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Ricochet</v>
+        <v>Superbloom</v>
       </c>
       <c r="G102" t="str">
-        <v>3:34</v>
+        <v>2:57</v>
       </c>
       <c r="H102" t="str">
-        <v>Snail Mail</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L102" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="103">
@@ -4692,13 +4692,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>prom queen</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-26</v>
@@ -4707,25 +4707,25 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>prom queen - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G114" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Amelia Moore</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L114" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="115">
@@ -4806,13 +4806,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ocean In The Desert</v>
+        <v>prom queen</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-26</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:44</v>
+        <v>2:43</v>
       </c>
       <c r="H117" t="str">
-        <v>Dionne Warwick</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L117" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-26</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>I Built You A Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H118" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L118" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2.0</v>
+        <v>Riptides</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-26</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ARIRANG</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G119" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H119" t="str">
-        <v>BTS</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L119" t="str">
-        <v>2.0 - BTS</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>6IXER PARTY</v>
+        <v>2.0</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-26</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>6WA</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H120" t="str">
-        <v>BigXthaPlug</v>
+        <v>BTS</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L120" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Highest</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-26</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Detour</v>
+        <v>6WA</v>
       </c>
       <c r="G121" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Samara Cyn</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L121" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Highest</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-26</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G122" t="str">
-        <v>2:40</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Coi Leray</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L122" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>So What</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-26</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:31</v>
+        <v>2:40</v>
       </c>
       <c r="H123" t="str">
-        <v>MUNA</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L123" t="str">
-        <v>So What - MUNA</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>So What</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-26</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>4:31</v>
       </c>
       <c r="H124" t="str">
-        <v>Eli</v>
+        <v>MUNA</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L124" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Running To Pain</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-26</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>So Help Me God</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G125" t="str">
-        <v>4:06</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Kelsey Lu</v>
+        <v>Eli</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L125" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-26</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H126" t="str">
-        <v>Anitta</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L126" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-26</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Big Mama</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:20</v>
+        <v>2:14</v>
       </c>
       <c r="H127" t="str">
-        <v>Latto</v>
+        <v>Anitta</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L127" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Bird Flu</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-26</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Big Mama</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H128" t="str">
-        <v>6LACK</v>
+        <v>Latto</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L128" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Lighter</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-26</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G129" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H129" t="str">
-        <v>Jelly Roll</v>
+        <v>6LACK</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L129" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Wide Awake</v>
+        <v>Lighter</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-26</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:16</v>
+        <v>2:59</v>
       </c>
       <c r="H130" t="str">
-        <v>Chris Stussy</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L130" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-26</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H131" t="str">
-        <v>Lizzo</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L131" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-26</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H132" t="str">
-        <v>Niall Horan</v>
+        <v>Lizzo</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L132" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>NORMAL</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-26</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>ARIRANG</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G133" t="str">
-        <v>3:01</v>
+        <v>2:34</v>
       </c>
       <c r="H133" t="str">
-        <v>BTS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L133" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Die Living</v>
+        <v>NORMAL</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-26</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Die Living - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H134" t="str">
-        <v>ILLENIUM</v>
+        <v>BTS</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L134" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Heaven On Earth</v>
+        <v>Die Living</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-26</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H135" t="str">
-        <v>Pentatonix</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L135" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>an apple a day</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-26</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>an apple a day - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>5:16</v>
+        <v>2:59</v>
       </c>
       <c r="H136" t="str">
-        <v>horsegiirL</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L136" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>OUT LATE.</v>
+        <v>an apple a day</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-26</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:09</v>
+        <v>5:16</v>
       </c>
       <c r="H137" t="str">
-        <v>Loud Luxury</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L137" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Be With You</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-26</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Wow! Signal</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:35</v>
+        <v>2:09</v>
       </c>
       <c r="H138" t="str">
-        <v>Muse</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L138" t="str">
-        <v>Be With You - Muse</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>First Red Rays</v>
+        <v>Be With You</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-26</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G139" t="str">
-        <v>8:27</v>
+        <v>3:35</v>
       </c>
       <c r="H139" t="str">
-        <v>Neurosis</v>
+        <v>Muse</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L139" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-26</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G140" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H140" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L140" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-26</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G141" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H141" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L141" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-26</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L142" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-26</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G143" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H143" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L143" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-26</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H144" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L144" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-26</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G145" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H145" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L145" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-26</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H146" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L146" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-26</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H147" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L147" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-26</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L148" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-26</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H149" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L149" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>if i am me, then who are you?</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-26</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>if i am me, then who are you? - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G150" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H150" t="str">
-        <v>PIAO</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/piao/1633160112</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L150" t="str">
-        <v>if i am me, then who are you? - PIAO</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>if i am me, then who are you?</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-26</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>if i am me, then who are you? - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H151" t="str">
-        <v>Kid Cudi</v>
+        <v>PIAO</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/piao/1633160112</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
       </c>
       <c r="L151" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>if i am me, then who are you? - PIAO</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-26</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L152" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-26</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G153" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H153" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L153" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-26</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H154" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L154" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-26</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G155" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H155" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L155" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-26</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G156" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H156" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L156" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-26</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G157" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H157" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L157" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-26</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G158" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L158" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-26</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G159" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H159" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L159" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-26</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L160" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-26</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G161" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L161" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-26</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H162" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L162" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-26</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H163" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L163" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-26</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G164" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H164" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L164" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-26</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L165" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-26</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H166" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L166" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-26</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H167" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L167" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-26</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H168" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L168" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-26</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L169" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-26</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H170" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L170" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-26</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G171" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H171" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L171" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-26</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G172" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H172" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L172" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-26</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G173" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H173" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L173" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-26</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H174" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L174" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-26</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H175" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L175" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-26</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G176" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H176" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L176" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-26</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H177" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L177" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-26</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G178" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H178" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L178" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-26</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H179" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L179" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-26</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H180" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L180" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-26</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H181" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L181" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-26</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G182" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H182" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L182" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-26</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L183" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-26</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L184" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-26</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H185" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L185" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-26</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H186" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L186" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-26</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G187" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H187" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L187" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-26</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G188" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H188" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L188" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-26</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H189" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L189" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-26</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H190" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L190" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-26</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H191" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L191" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-26</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L192" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-26</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H193" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L193" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-26</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H194" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L194" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-26</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G195" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H195" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L195" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-26</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H196" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L196" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-26</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G197" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H197" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L197" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-26</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H198" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L198" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-26</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H199" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L199" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-26</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H200" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L200" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-26</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H201" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L201" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-26</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H202" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L202" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-26</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H203" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L203" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-26</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H204" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L204" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-26</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H205" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L205" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-26</v>
@@ -8203,68 +8203,106 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H206" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L206" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D207" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
+      <c r="D208" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G207" t="str">
+      <c r="G208" t="str">
         <v>5:19</v>
       </c>
-      <c r="H207" t="str">
+      <c r="H208" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K207" t="str">
+      <c r="K208" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L207" t="str">
+      <c r="L208" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -1997,7 +1997,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -3213,7 +3213,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -3175,7 +3175,7 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1959,7 +1959,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:17</v>
+        <v>3:56</v>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:31</v>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v>Nick Carter</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:38</v>
+        <v>3:42</v>
       </c>
       <c r="H4" t="str">
-        <v>Carly Pearce</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>10 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:11</v>
+        <v>2:16</v>
       </c>
       <c r="H5" t="str">
-        <v>OneRepublic</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H6" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:47</v>
+        <v>3:38</v>
       </c>
       <c r="H7" t="str">
-        <v>Armin van Buuren</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>7:10</v>
+        <v>3:01</v>
       </c>
       <c r="H8" t="str">
-        <v>David Gilmour</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:06</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Grace Enger</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:05</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Loreen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>13 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>13 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v>2:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Freya Ridings</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>13 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>13 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H12" t="str">
-        <v>David Gilmour</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:28</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:31</v>
+        <v>6:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Martin Garrix</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:11</v>
+        <v>4:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Baby Queen</v>
+        <v>Eagles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>13 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:27</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:51</v>
+        <v>4:00</v>
       </c>
       <c r="H20" t="str">
-        <v>Rick Astley</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:39</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>13 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>13 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:08</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie J</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>Bishop Briggs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:42</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>twocolors</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>13 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:31</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Luke Combs</v>
+        <v>Prince</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>5:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Allison Russell</v>
+        <v>RAYE</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>We Three</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>3:18</v>
       </c>
       <c r="H29" t="str">
-        <v>paris jackson</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Kane Brown</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:37</v>
+        <v>5:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Lainey Wilson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:57</v>
+        <v>2:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Malcolm Todd</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>2:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:29</v>
+        <v>2:40</v>
       </c>
       <c r="H34" t="str">
-        <v>Kungs</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:28</v>
+        <v>3:30</v>
       </c>
       <c r="H35" t="str">
-        <v>Sunday (1994)</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>4:02</v>
       </c>
       <c r="H36" t="str">
-        <v>aron!</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:51</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:49</v>
+        <v>2:22</v>
       </c>
       <c r="H38" t="str">
-        <v>Sunday (1994)</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:16</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>Owen Riegling</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:16</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>LANY</v>
+        <v>Cannons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:25</v>
+        <v>4:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Maverick Sabre</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>4:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Amanda Jordan</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:57</v>
+        <v>2:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Beabadoobee</v>
+        <v>aron!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:58</v>
+        <v>4:00</v>
       </c>
       <c r="H44" t="str">
-        <v>Spacey Jane</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>3:56</v>
       </c>
       <c r="H45" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>DMA'S</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:09</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>Mei Semones</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:08</v>
+        <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>The Lemon Twigs</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Natalie Jane</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:57</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>Far Caspian</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:34</v>
+        <v>3:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Celine Dion</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:48</v>
+        <v>7:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Harry Styles</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:58</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:33</v>
+        <v>3:05</v>
       </c>
       <c r="H55" t="str">
-        <v>Ellise</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:01</v>
+        <v>3:12</v>
       </c>
       <c r="H56" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:56</v>
+        <v>9:11</v>
       </c>
       <c r="H57" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:54</v>
+        <v>3:49</v>
       </c>
       <c r="H58" t="str">
-        <v>Bebe Rexha</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>NathanEvanss</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>3:31</v>
       </c>
       <c r="H60" t="str">
-        <v>R3HAB</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:16</v>
+        <v>2:27</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Johnny Orlando</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:29</v>
+        <v>2:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Russell Dickerson</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>2:39</v>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:01</v>
+        <v>5:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Mike Posner</v>
+        <v>Jessie J</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:23</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:39</v>
+        <v>2:42</v>
       </c>
       <c r="H69" t="str">
-        <v>almost monday</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:04</v>
+        <v>2:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>vaultboy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:49</v>
+        <v>3:22</v>
       </c>
       <c r="H72" t="str">
-        <v>The Warning</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>aron! - Wonderful Thing (City View)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:14</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>aron!</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>aron! - Wonderful Thing (City View) - aron!</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:43</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>paris jackson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:43</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>Sting</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:44</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Dean Lewis</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:52</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>Cannons</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:13</v>
+        <v>4:29</v>
       </c>
       <c r="H79" t="str">
-        <v>Kim Petras</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:19</v>
+        <v>4:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:31</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Kiana Ledé</v>
+        <v>aron!</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>Ringo Starr</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>2:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Maya Hawke</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:55</v>
+        <v>4:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Armin van Buuren</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:52</v>
+        <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Demi Lovato</v>
+        <v>LANY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:53</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Peter Gabriel</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:30</v>
+        <v>2:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie J</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:18</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Harry Styles</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>7:20</v>
+        <v>3:58</v>
       </c>
       <c r="H89" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>BRITs</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>2:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:11</v>
+        <v>2:57</v>
       </c>
       <c r="H93" t="str">
-        <v>The Kiffness</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>Lauv</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:03</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>RAYE</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:50</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Armik</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:53</v>
+        <v>3:34</v>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H98" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:32</v>
+        <v>4:58</v>
       </c>
       <c r="H99" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>2:33</v>
       </c>
       <c r="H100" t="str">
-        <v>Girl Tones</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:40</v>
+        <v>5:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,97 +4231,97 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Automatic</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Superbloom</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G102" t="str">
-        <v>2:57</v>
+        <v>3:18</v>
       </c>
       <c r="H102" t="str">
-        <v>Jessie Ware</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L102" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SWIM</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ARIRANG</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>2:39</v>
+        <v>2:47</v>
       </c>
       <c r="H103" t="str">
-        <v>BTS</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L103" t="str">
-        <v>SWIM - BTS</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4330,7 +4330,7 @@
         <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>5:01</v>
+        <v>6:17</v>
       </c>
       <c r="H104" t="str">
         <v>RAYE</v>
@@ -4342,3962 +4342,3962 @@
         <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Loving Life Again</v>
+        <v>MARATHON</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dandelion</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:46</v>
+        <v>2:49</v>
       </c>
       <c r="H105" t="str">
-        <v>Ella Langley</v>
+        <v>Becky G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L105" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Rethink Some Things</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>Sexistential</v>
       </c>
       <c r="G106" t="str">
-        <v>2:45</v>
+        <v>3:34</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Robyn</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L106" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TRANKAITO</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:42</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Feid</v>
+        <v>John Summit</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L107" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Leak It</v>
+        <v>Sideways</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Leak It - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G108" t="str">
-        <v>3:03</v>
+        <v>3:12</v>
       </c>
       <c r="H108" t="str">
-        <v>FLO</v>
+        <v>ZAYN</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L108" t="str">
-        <v>Leak It - FLO</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>LUVAGIRL</v>
+        <v>Lose Control</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G109" t="str">
-        <v>2:40</v>
+        <v>2:39</v>
       </c>
       <c r="H109" t="str">
-        <v>Coco Jones</v>
+        <v>Yeat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L109" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>D33P3R</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>R3SET</v>
+        <v>Zavier</v>
       </c>
       <c r="G110" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L110" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G111" t="str">
-        <v>3:01</v>
+        <v>2:07</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Central Cee</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L111" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Don't Hate Me</v>
+        <v>Automatic</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G112" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H112" t="str">
-        <v>Miles Caton</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L112" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>PONGO</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>PONGO - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>3:34</v>
       </c>
       <c r="H113" t="str">
-        <v>Rvssian</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L113" t="str">
-        <v>PONGO - Rvssian</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tractor Beam</v>
+        <v>prom queen</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Ricochet</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H114" t="str">
-        <v>Snail Mail</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L114" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>BOTERO</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>BOTERO - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:14</v>
+        <v>3:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Maluma</v>
+        <v>J Balvin</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L115" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Distance</v>
+        <v>Phoenix</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Distance - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v>2:24</v>
       </c>
       <c r="H116" t="str">
-        <v>Finn Askew</v>
+        <v>Marshmello</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L116" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>prom queen</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>prom queen - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:43</v>
+        <v>2:56</v>
       </c>
       <c r="H117" t="str">
-        <v>Amelia Moore</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L117" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:44</v>
+        <v>3:36</v>
       </c>
       <c r="H118" t="str">
-        <v>Dionne Warwick</v>
+        <v>Eli</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L118" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Riptides</v>
+        <v>Lonely</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Built You A Tower</v>
+        <v>Ö</v>
       </c>
       <c r="G119" t="str">
-        <v>3:17</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Fcukers</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L119" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2.0</v>
+        <v>Back in Love</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>ARIRANG</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:49</v>
+        <v>3:14</v>
       </c>
       <c r="H120" t="str">
-        <v>BTS</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L120" t="str">
-        <v>2.0 - BTS</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>6IXER PARTY</v>
+        <v>Sideways</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>6WA</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G121" t="str">
-        <v>3:08</v>
+        <v>3:55</v>
       </c>
       <c r="H121" t="str">
-        <v>BigXthaPlug</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L121" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Highest</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Detour</v>
+        <v>Honora</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>4:22</v>
       </c>
       <c r="H122" t="str">
-        <v>Samara Cyn</v>
+        <v>Flea</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L122" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:40</v>
+        <v>2:58</v>
       </c>
       <c r="H123" t="str">
-        <v>Coi Leray</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L123" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>So What</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:31</v>
+        <v>3:02</v>
       </c>
       <c r="H124" t="str">
-        <v>MUNA</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L124" t="str">
-        <v>So What - MUNA</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>4:42</v>
       </c>
       <c r="H125" t="str">
-        <v>Eli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L125" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Running To Pain</v>
+        <v>wasteland</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>So Help Me God</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:06</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
-        <v>Kelsey Lu</v>
+        <v>Yuna</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L126" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G127" t="str">
-        <v>2:14</v>
+        <v>2:31</v>
       </c>
       <c r="H127" t="str">
-        <v>Anitta</v>
+        <v>Artemas</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L127" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Por LA</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Big Mama</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G128" t="str">
-        <v>4:20</v>
+        <v>2:19</v>
       </c>
       <c r="H128" t="str">
-        <v>Latto</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L128" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Bird Flu</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G129" t="str">
-        <v>2:58</v>
+        <v>4:14</v>
       </c>
       <c r="H129" t="str">
-        <v>6LACK</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L129" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Lighter</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G130" t="str">
-        <v>2:59</v>
+        <v>4:18</v>
       </c>
       <c r="H130" t="str">
-        <v>Jelly Roll</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L130" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Wide Awake</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:16</v>
+        <v>2:54</v>
       </c>
       <c r="H131" t="str">
-        <v>Chris Stussy</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L131" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:25</v>
+        <v>2:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Lizzo</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L132" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Dinner Party</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Dinner Party</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G133" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Niall Horan</v>
+        <v>ERNEST</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L133" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>NORMAL</v>
+        <v>Special</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>ARIRANG</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G134" t="str">
-        <v>3:01</v>
+        <v>2:49</v>
       </c>
       <c r="H134" t="str">
-        <v>BTS</v>
+        <v>Elmiene</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L134" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Die Living</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Die Living - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G135" t="str">
-        <v>2:50</v>
+        <v>2:52</v>
       </c>
       <c r="H135" t="str">
-        <v>ILLENIUM</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L135" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Heaven On Earth</v>
+        <v>STAY</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H136" t="str">
-        <v>Pentatonix</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L136" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>an apple a day</v>
+        <v>Unglued</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>an apple a day - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G137" t="str">
-        <v>5:16</v>
+        <v>3:54</v>
       </c>
       <c r="H137" t="str">
-        <v>horsegiirL</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L137" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>OUT LATE.</v>
+        <v>Ritual</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:09</v>
+        <v>3:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Loud Luxury</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L138" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Be With You</v>
+        <v>The Best</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Wow! Signal</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:35</v>
+        <v>3:48</v>
       </c>
       <c r="H139" t="str">
-        <v>Muse</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L139" t="str">
-        <v>Be With You - Muse</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>First Red Rays</v>
+        <v>Smile</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>8:27</v>
+        <v>3:50</v>
       </c>
       <c r="H140" t="str">
-        <v>Neurosis</v>
+        <v>Two Shell</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L140" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Caught In The Echo</v>
+        <v>Duro</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>4:02</v>
+        <v>3:05</v>
       </c>
       <c r="H141" t="str">
-        <v>Foo Fighters</v>
+        <v>Skrillex</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L141" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Little by Little</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Little by Little - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G142" t="str">
-        <v>2:34</v>
+        <v>2:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Mon Rovîa</v>
+        <v>Sublime</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L142" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Montgomery County</v>
+        <v>Carousel</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G143" t="str">
-        <v>3:28</v>
+        <v>3:36</v>
       </c>
       <c r="H143" t="str">
-        <v>Parker McCollum</v>
+        <v>Cannons</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L143" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Dive Into Me</v>
+        <v>Mercy</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>3:49</v>
       </c>
       <c r="H144" t="str">
-        <v>Alok</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L144" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>more than just a little bit</v>
+        <v>Palms</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>getting up to no good</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H145" t="str">
-        <v>Artemas</v>
+        <v>The Maine</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L145" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>WORSHIP</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>WORSHIP - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G146" t="str">
-        <v>2:43</v>
+        <v>5:28</v>
       </c>
       <c r="H146" t="str">
-        <v>Asake</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L146" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Honest</v>
+        <v>Danger</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Honest - Single</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:22</v>
+        <v>2:19</v>
       </c>
       <c r="H147" t="str">
-        <v>Ebony Riley</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L147" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>6ft Under</v>
+        <v>Icarus</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>6ft Under - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>4:25</v>
       </c>
       <c r="H148" t="str">
-        <v>KELS</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L148" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Maybe Again</v>
+        <v>idk idk</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>When The City Sleeps</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:29</v>
+        <v>2:26</v>
       </c>
       <c r="H149" t="str">
-        <v>Alex Isley</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L149" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Trigger Happy</v>
+        <v>Tonight</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Attachment Theory</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:01</v>
+        <v>2:25</v>
       </c>
       <c r="H150" t="str">
-        <v>Aubrie Sellers</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L150" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>if i am me, then who are you?</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-i-am-me-then-who-are-you/1878473322</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>if i am me, then who are you? - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G151" t="str">
-        <v>2:57</v>
+        <v>3:44</v>
       </c>
       <c r="H151" t="str">
-        <v>PIAO</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/piao/1633160112</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-i-am-me-then-who-are-you/1878473318</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L151" t="str">
-        <v>if i am me, then who are you? - PIAO</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>2:45</v>
       </c>
       <c r="H152" t="str">
-        <v>Kid Cudi</v>
+        <v>BIA</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L152" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G153" t="str">
-        <v>3:30</v>
+        <v>3:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Swae Lee</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L153" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Runnin' On E</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G154" t="str">
-        <v>2:27</v>
+        <v>3:44</v>
       </c>
       <c r="H154" t="str">
-        <v>Wyatt Flores</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L154" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>FREESTYLE</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>LINAJE</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G155" t="str">
-        <v>5:36</v>
+        <v>2:41</v>
       </c>
       <c r="H155" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L155" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Orcasitas</v>
+        <v>R3verse</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Alma De Cántaro</v>
+        <v>takeaways</v>
       </c>
       <c r="G156" t="str">
-        <v>3:23</v>
+        <v>3:31</v>
       </c>
       <c r="H156" t="str">
-        <v>marquitos</v>
+        <v>Medium Build</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L156" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Vida Loca</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>FREE SPIRITS</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G157" t="str">
-        <v>2:35</v>
+        <v>2:32</v>
       </c>
       <c r="H157" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>MIKE</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L157" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Honest</v>
+        <v>heart of gold</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Weight of the Woods</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>2:51</v>
       </c>
       <c r="H158" t="str">
-        <v>Dermot Kennedy</v>
+        <v>kai devega</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L158" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Skeletor</v>
       </c>
       <c r="G159" t="str">
-        <v>3:01</v>
+        <v>4:21</v>
       </c>
       <c r="H159" t="str">
-        <v>Kenia Os</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L159" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Dream House</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Peaches!</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>5:00</v>
+        <v>2:54</v>
       </c>
       <c r="H160" t="str">
-        <v>The Black Keys</v>
+        <v>Empress Of</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L160" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Light as a Feather</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Everything Glows</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>2:51</v>
       </c>
       <c r="H161" t="str">
-        <v>Cannons</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L161" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loving One</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Loving One - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:39</v>
+        <v>2:37</v>
       </c>
       <c r="H162" t="str">
-        <v>People I’ve Met</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L162" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Both Can Be True</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G163" t="str">
-        <v>3:05</v>
+        <v>4:05</v>
       </c>
       <c r="H163" t="str">
-        <v>Trousdale</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L163" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Buffalo 66</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>4:27</v>
+        <v>3:46</v>
       </c>
       <c r="H164" t="str">
-        <v>Nessa Barrett</v>
+        <v>Benny G</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L164" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>brb</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>brb - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:36</v>
+        <v>3:03</v>
       </c>
       <c r="H165" t="str">
-        <v>The Two Lips</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L165" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Euphoria</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Euphoria - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>3:32</v>
+        <v>4:19</v>
       </c>
       <c r="H166" t="str">
-        <v>Talia Rae</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L166" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>if i'm lucky</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>better late than not at all - EP</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:57</v>
+        <v>2:10</v>
       </c>
       <c r="H167" t="str">
-        <v>Chelsea Jordan</v>
+        <v>WesGhost</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L167" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Gracie</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>F.I.G</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H168" t="str">
-        <v>Naomi Scott</v>
+        <v>GERD</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L168" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>down under</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>down under - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H169" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Prospa</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L169" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Send Me A Sign</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H170" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L170" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Breathe</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:02</v>
+        <v>2:48</v>
       </c>
       <c r="H171" t="str">
-        <v>OneRepublic</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L171" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Dream Chaser</v>
+        <v>xs</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Dream Chaser</v>
+        <v>xs - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:14</v>
+        <v>3:19</v>
       </c>
       <c r="H172" t="str">
-        <v>Willie Nelson</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L172" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Trouble</v>
+        <v>Sail</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Girlfriend</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G173" t="str">
-        <v>3:17</v>
+        <v>4:54</v>
       </c>
       <c r="H173" t="str">
-        <v>Grace Ives</v>
+        <v>Future Islands</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L173" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>judas</v>
+        <v>Dreamin'</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/dreamin/1886158585</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>judas - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G174" t="str">
-        <v>3:31</v>
+        <v>3:33</v>
       </c>
       <c r="H174" t="str">
-        <v>Josiah Queen</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/dreamin/1886158441</v>
       </c>
       <c r="L174" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Dreamin' - Ashley Monroe</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>JINX</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>JINX - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G175" t="str">
-        <v>2:54</v>
+        <v>2:39</v>
       </c>
       <c r="H175" t="str">
-        <v>Zacari</v>
+        <v>Armanii</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L175" t="str">
-        <v>JINX - Zacari</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>se fue</v>
+        <v>La Opinión</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Náufrago</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G176" t="str">
-        <v>2:51</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Eddy</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L176" t="str">
-        <v>se fue - Eddy</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>The Blade</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>The Blade - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H177" t="str">
-        <v>Kingfishr</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L177" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Metric Rules</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:13</v>
+        <v>2:43</v>
       </c>
       <c r="H178" t="str">
-        <v>SPINALL</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L178" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:15</v>
+        <v>2:16</v>
       </c>
       <c r="H179" t="str">
-        <v>ZEP</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L179" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H180" t="str">
-        <v>Hutch</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L180" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Me Neither</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G181" t="str">
-        <v>5:15</v>
+        <v>3:32</v>
       </c>
       <c r="H181" t="str">
-        <v>MJ Cole</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L181" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cyclone</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Loss</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G182" t="str">
-        <v>5:33</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Gaerea</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L182" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checkmate</v>
+        <v>Wonder</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Checkmate - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:23</v>
+        <v>3:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Blue Medusa</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L183" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>DAVE</v>
+        <v>Icu</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>DAVE - Single</v>
+        <v>Icu - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>2:53</v>
       </c>
       <c r="H184" t="str">
-        <v>Hulvey</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L184" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Icu - Joseph O'Brien</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Change</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Change - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G185" t="str">
-        <v>2:38</v>
+        <v>2:45</v>
       </c>
       <c r="H185" t="str">
-        <v>Stephen Stanley</v>
+        <v>Jozzy</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L185" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Te Entiendo</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:05</v>
+        <v>3:21</v>
       </c>
       <c r="H186" t="str">
-        <v>Maisak</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L186" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>CHEVROLET 90</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>V</v>
+        <v>Rise</v>
       </c>
       <c r="G187" t="str">
-        <v>2:01</v>
+        <v>4:02</v>
       </c>
       <c r="H187" t="str">
-        <v>Rey Quinto</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L187" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tirabalas</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:53</v>
+        <v>3:51</v>
       </c>
       <c r="H188" t="str">
-        <v>Hans el Oso</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L188" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>punchbowl</v>
+        <v>Delicately</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>punchbowl - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:34</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>Julio Caesar</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L189" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Wild Ride</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Wild Ride - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:41</v>
+        <v>3:27</v>
       </c>
       <c r="H190" t="str">
-        <v>Durand Bernarr</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L190" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Lamb Chop</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G191" t="str">
-        <v>2:03</v>
+        <v>6:04</v>
       </c>
       <c r="H191" t="str">
-        <v>Chuckyy</v>
+        <v>José González</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L191" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Free Nick</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Free Nick - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G192" t="str">
-        <v>2:05</v>
+        <v>3:33</v>
       </c>
       <c r="H192" t="str">
-        <v>Raq baby</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L192" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Make Me Brand New</v>
+        <v>Daisy</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:06</v>
+        <v>3:02</v>
       </c>
       <c r="H193" t="str">
-        <v>Dante’ Pride</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L193" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Define You</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Define You - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G194" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>Luca Fogale</v>
+        <v>james K</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L194" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>If You Change</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Roses</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:41</v>
+        <v>2:45</v>
       </c>
       <c r="H195" t="str">
-        <v>Widowspeak</v>
+        <v>MAVICA</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L195" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>What I See</v>
+        <v>Fort</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:32</v>
+        <v>2:27</v>
       </c>
       <c r="H196" t="str">
-        <v>See You Next Year</v>
+        <v>Lamb</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L196" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Witching Hour</v>
+        <v>SAME LA</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Butterfly</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H197" t="str">
-        <v>Witch Post</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L197" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Actin' Tough</v>
+        <v>Working On It</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:07</v>
+        <v>3:06</v>
       </c>
       <c r="H198" t="str">
-        <v>Dean Turnley</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L198" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:52</v>
+        <v>4:03</v>
       </c>
       <c r="H199" t="str">
-        <v>Anais Cardot</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L199" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Rewind It</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Rewind It - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>1:34</v>
+        <v>3:26</v>
       </c>
       <c r="H200" t="str">
-        <v>Nino Paid</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L200" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Turn It Up</v>
+        <v>Simple Things</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:33</v>
+        <v>3:46</v>
       </c>
       <c r="H201" t="str">
-        <v>slayr</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L201" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Down</v>
+        <v>Want It Back</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Down - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:08</v>
+        <v>3:27</v>
       </c>
       <c r="H202" t="str">
-        <v>MexikoDro</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L202" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Make It Out</v>
+        <v>Bite Down</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Make It Out - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:17</v>
+        <v>3:36</v>
       </c>
       <c r="H203" t="str">
-        <v>Trueblood</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L203" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>better than boston</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>better than boston - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G204" t="str">
-        <v>3:02</v>
+        <v>5:42</v>
       </c>
       <c r="H204" t="str">
-        <v>Tom Siletto</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L204" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>Demons</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G205" t="str">
-        <v>2:34</v>
+        <v>2:42</v>
       </c>
       <c r="H205" t="str">
-        <v>Lost Frequencies</v>
+        <v>Anella</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L205" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>All I Need</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>All I Need - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:06</v>
+        <v>3:35</v>
       </c>
       <c r="H206" t="str">
-        <v>GRiZ</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L206" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Weeping Tones</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Peace In Place</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>2:59</v>
+        <v>3:49</v>
       </c>
       <c r="H207" t="str">
-        <v>Poison the Well</v>
+        <v>Enslaved</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L207" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Promise You This</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E208" t="str">
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Goliath</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G208" t="str">
-        <v>5:19</v>
+        <v>4:09</v>
       </c>
       <c r="H208" t="str">
-        <v>Exodus</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L208" t="str">
-        <v>Promise You This - Exodus</v>
+        <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:56</v>
@@ -477,7 +477,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:50</v>
@@ -515,7 +515,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:42</v>
@@ -553,7 +553,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:16</v>
@@ -591,7 +591,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:08</v>
@@ -629,7 +629,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:38</v>
@@ -667,7 +667,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:01</v>
@@ -705,7 +705,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:59</v>
@@ -743,7 +743,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:59</v>
@@ -781,7 +781,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:58</v>
@@ -819,7 +819,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:49</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:56</v>
@@ -477,7 +477,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:50</v>
@@ -515,7 +515,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:42</v>
@@ -553,7 +553,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:16</v>
@@ -591,7 +591,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:08</v>
@@ -629,7 +629,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:38</v>
@@ -667,7 +667,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:01</v>
@@ -705,7 +705,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:59</v>
@@ -743,7 +743,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:59</v>
@@ -781,7 +781,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:58</v>
@@ -819,7 +819,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:49</v>
@@ -971,7 +971,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:52</v>
@@ -1009,7 +1009,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1161,7 +1161,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:35</v>
@@ -1199,7 +1199,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:01</v>
@@ -1237,7 +1237,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:40</v>
@@ -1275,7 +1275,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:25</v>
@@ -1313,7 +1313,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:42</v>
@@ -1427,7 +1427,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:30</v>
@@ -1465,7 +1465,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:18</v>
@@ -1503,7 +1503,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:33</v>
@@ -1541,7 +1541,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:53</v>
@@ -2149,7 +2149,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:17</v>
@@ -2301,7 +2301,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:57</v>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:47</v>
@@ -2377,7 +2377,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>7:10</v>
@@ -2453,7 +2453,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:05</v>
@@ -2491,7 +2491,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:12</v>
@@ -2529,7 +2529,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v>9:11</v>
@@ -2567,7 +2567,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:49</v>
@@ -2605,7 +2605,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:28</v>
@@ -2643,7 +2643,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:31</v>
@@ -2681,7 +2681,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:11</v>
@@ -2719,7 +2719,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v>2:27</v>
@@ -2757,7 +2757,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:34</v>
@@ -2795,7 +2795,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:50</v>
@@ -2833,7 +2833,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:51</v>
@@ -2871,7 +2871,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:39</v>
@@ -2909,7 +2909,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v>5:08</v>
@@ -4087,7 +4087,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:48</v>
@@ -6972,13 +6972,13 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Dreamin'</v>
+        <v>Dreaming</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dreamin/1886158585</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-27</v>
@@ -7002,10 +7002,10 @@
         <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dreamin/1886158441</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L174" t="str">
-        <v>Dreamin' - Ashley Monroe</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="175">
@@ -7352,7 +7352,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Icu</v>
+        <v>ICU</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -7367,7 +7367,7 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Icu - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G184" t="str">
         <v>2:53</v>
@@ -7385,7 +7385,7 @@
         <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L184" t="str">
-        <v>Icu - Joseph O'Brien</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="185">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:56</v>
@@ -477,7 +477,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:50</v>
@@ -515,7 +515,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:42</v>
@@ -553,7 +553,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:16</v>
@@ -591,7 +591,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:08</v>
@@ -629,7 +629,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:38</v>
@@ -667,7 +667,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:01</v>
@@ -705,7 +705,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:59</v>
@@ -743,7 +743,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:59</v>
@@ -857,7 +857,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:22</v>
@@ -895,7 +895,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:50</v>
@@ -933,7 +933,7 @@
         <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>6:43</v>
@@ -1389,7 +1389,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>5:12</v>
@@ -2111,7 +2111,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:17</v>
@@ -2263,7 +2263,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:11</v>
@@ -2415,7 +2415,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:06</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:56</v>
@@ -477,19 +477,19 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:50</v>
@@ -515,19 +515,19 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:42</v>
@@ -553,19 +553,19 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:16</v>
@@ -591,19 +591,19 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:08</v>
@@ -629,19 +629,19 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:38</v>
@@ -667,19 +667,19 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:01</v>
@@ -705,19 +705,19 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:59</v>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:28</v>
@@ -1085,19 +1085,19 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:01</v>
@@ -1123,19 +1123,19 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:00</v>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:56</v>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:37</v>
@@ -1617,19 +1617,19 @@
         <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:26</v>
@@ -1655,19 +1655,19 @@
         <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>2:40</v>
@@ -1693,19 +1693,19 @@
         <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:30</v>
@@ -1731,19 +1731,19 @@
         <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>4:02</v>
@@ -1769,19 +1769,19 @@
         <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:40</v>
@@ -1807,19 +1807,19 @@
         <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:22</v>
@@ -1845,19 +1845,19 @@
         <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:47</v>
@@ -1883,19 +1883,19 @@
         <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:39</v>
@@ -1921,19 +1921,19 @@
         <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:10</v>
@@ -1959,19 +1959,19 @@
         <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:47</v>
@@ -1997,19 +1997,19 @@
         <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:14</v>
@@ -2035,19 +2035,19 @@
         <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>4:00</v>
@@ -2073,19 +2073,19 @@
         <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:56</v>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:31</v>
@@ -2225,19 +2225,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:38</v>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:58</v>
@@ -4163,19 +4163,19 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>2:33</v>
@@ -4201,19 +4201,19 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>5:01</v>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -8235,7 +8235,7 @@
         <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E207" t="str">
         <v/>
@@ -8273,7 +8273,7 @@
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E208" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -781,7 +781,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:58</v>
@@ -819,7 +819,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:49</v>
@@ -971,7 +971,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:52</v>
@@ -1009,7 +1009,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1275,7 +1275,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:25</v>
@@ -1313,7 +1313,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:42</v>
@@ -1427,7 +1427,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:30</v>
@@ -1465,7 +1465,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:18</v>
@@ -1503,7 +1503,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:33</v>
@@ -1541,7 +1541,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:53</v>
@@ -2149,7 +2149,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:17</v>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -1161,7 +1161,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:35</v>
@@ -1199,7 +1199,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:01</v>
@@ -1237,7 +1237,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:40</v>
@@ -2301,7 +2301,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:57</v>
@@ -2377,7 +2377,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>7:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -743,7 +743,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:59</v>
@@ -857,7 +857,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:22</v>
@@ -895,7 +895,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:50</v>
@@ -933,7 +933,7 @@
         <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>6:43</v>
@@ -1389,7 +1389,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>5:12</v>
@@ -2111,7 +2111,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:17</v>
@@ -2263,7 +2263,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:11</v>
@@ -4388,13 +4388,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Sucker For Love</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-28</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Sexistential</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>Robyn</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L106" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ALL THE TIME</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-28</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H107" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L107" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Sideways</v>
+        <v>FATHER</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-28</v>
@@ -4479,25 +4479,25 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>KONNAKOL</v>
+        <v>BULLY</v>
       </c>
       <c r="G108" t="str">
-        <v>3:12</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>ZAYN</v>
+        <v>Kanye West</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L108" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="109">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Automatic</v>
+        <v>Sideways</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-28</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Superbloom</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G112" t="str">
-        <v>2:57</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Jessie Ware</v>
+        <v>ZAYN</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L112" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Tractor Beam</v>
+        <v>Automatic</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-28</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Ricochet</v>
+        <v>Superbloom</v>
       </c>
       <c r="G113" t="str">
-        <v>3:34</v>
+        <v>2:57</v>
       </c>
       <c r="H113" t="str">
-        <v>Snail Mail</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L113" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>prom queen</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-28</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>prom queen - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G114" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Amelia Moore</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L114" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Pal Agua</v>
+        <v>prom queen</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-28</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Pal Agua - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:26</v>
+        <v>2:43</v>
       </c>
       <c r="H115" t="str">
-        <v>J Balvin</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L115" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Phoenix</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-28</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Phoenix - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:24</v>
+        <v>3:26</v>
       </c>
       <c r="H116" t="str">
-        <v>Marshmello</v>
+        <v>J Balvin</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L116" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Phoenix</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-28</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:56</v>
+        <v>2:24</v>
       </c>
       <c r="H117" t="str">
-        <v>Ne-Yo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L117" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Feel Your Rain</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-28</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:36</v>
+        <v>2:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Eli</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L118" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Lonely</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-28</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ö</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Fcukers</v>
+        <v>Eli</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L119" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Back in Love</v>
+        <v>Lonely</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-28</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Back in Love - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G120" t="str">
-        <v>3:14</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Fcukers</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L120" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Sideways</v>
+        <v>Back in Love</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-28</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H121" t="str">
-        <v>Charlie Puth</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L121" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Sideways</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-28</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Honora</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G122" t="str">
-        <v>4:22</v>
+        <v>3:55</v>
       </c>
       <c r="H122" t="str">
-        <v>Flea</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L122" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-28</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G123" t="str">
-        <v>2:58</v>
+        <v>4:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Flea</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L123" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-28</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:02</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Honey Bxby</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L124" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>One Thing At A Time</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-28</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Creature of Habit</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:42</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Courtney Barnett</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L125" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>wasteland</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-28</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>wasteland - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>4:42</v>
       </c>
       <c r="H126" t="str">
-        <v>Yuna</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L126" t="str">
-        <v>wasteland - Yuna</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>wasteland</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-28</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>getting up to no good</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:31</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Artemas</v>
+        <v>Yuna</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L127" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Por LA</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-28</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>TODO Ø NADA</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G128" t="str">
-        <v>2:19</v>
+        <v>2:31</v>
       </c>
       <c r="H128" t="str">
-        <v>Linea Personal</v>
+        <v>Artemas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L128" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>You Lead Me</v>
+        <v>Por LA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-28</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G129" t="str">
-        <v>4:14</v>
+        <v>2:19</v>
       </c>
       <c r="H129" t="str">
-        <v>Lauren Daigle</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L129" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Just A Kid</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-28</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Broken View</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G130" t="str">
-        <v>4:18</v>
+        <v>4:14</v>
       </c>
       <c r="H130" t="str">
-        <v>Sam Barber</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L130" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Country And She Knows It</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-28</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G131" t="str">
-        <v>2:54</v>
+        <v>4:18</v>
       </c>
       <c r="H131" t="str">
-        <v>Luke Bryan</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L131" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-28</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:35</v>
+        <v>2:54</v>
       </c>
       <c r="H132" t="str">
-        <v>Thomas Rhett</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L132" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Deep Blue</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-28</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Deep Blue</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>ERNEST</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L133" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Special</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-28</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>sounds for someone</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G134" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Elmiene</v>
+        <v>ERNEST</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L134" t="str">
-        <v>Special - Elmiene</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Heart Attack</v>
+        <v>Special</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-28</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CANDY</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G135" t="str">
-        <v>2:52</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Justine Skye</v>
+        <v>Elmiene</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L135" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>STAY</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-28</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>STAY - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G136" t="str">
-        <v>3:06</v>
+        <v>2:52</v>
       </c>
       <c r="H136" t="str">
-        <v>Stray Kids</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L136" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Unglued</v>
+        <v>STAY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-28</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Work of Heart</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H137" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L137" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Ritual</v>
+        <v>Unglued</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-28</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Ritual - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G138" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Icona Pop</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L138" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>The Best</v>
+        <v>Ritual</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-28</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:48</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Conan Gray</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L139" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Smile</v>
+        <v>The Best</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-28</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Smile - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:50</v>
+        <v>3:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Two Shell</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L140" t="str">
-        <v>Smile - Two Shell</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Duro</v>
+        <v>Smile</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-28</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Duro - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Skrillex</v>
+        <v>Two Shell</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L141" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Duro</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-28</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H142" t="str">
-        <v>Sublime</v>
+        <v>Skrillex</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L142" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Carousel</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-28</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Everything Glows</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G143" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Cannons</v>
+        <v>Sublime</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L143" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Mercy</v>
+        <v>Carousel</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-28</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Mercy - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G144" t="str">
-        <v>3:49</v>
+        <v>3:36</v>
       </c>
       <c r="H144" t="str">
-        <v>PRESIDENT</v>
+        <v>Cannons</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L144" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Palms</v>
+        <v>Mercy</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-28</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Palms - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:18</v>
+        <v>3:49</v>
       </c>
       <c r="H145" t="str">
-        <v>The Maine</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L145" t="str">
-        <v>Palms - The Maine</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Ozzy's Song</v>
+        <v>Palms</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-28</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>5:28</v>
+        <v>3:18</v>
       </c>
       <c r="H146" t="str">
-        <v>Black Label Society</v>
+        <v>The Maine</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L146" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Danger</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-28</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Danger - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>2:19</v>
+        <v>5:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Nia Archives</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L147" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Icarus</v>
+        <v>Danger</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-28</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Icarus - Single</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:25</v>
+        <v>2:19</v>
       </c>
       <c r="H148" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L148" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>idk idk</v>
+        <v>Icarus</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-28</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>idk idk - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:26</v>
+        <v>4:25</v>
       </c>
       <c r="H149" t="str">
-        <v>Jim Legxacy</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L149" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Tonight</v>
+        <v>idk idk</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-28</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Tonight - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:25</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L150" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Tonight</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-28</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Switcheroo</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:44</v>
+        <v>2:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Gelli Haha</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L151" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-28</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G152" t="str">
-        <v>2:45</v>
+        <v>3:44</v>
       </c>
       <c r="H152" t="str">
-        <v>BIA</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L152" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>this girl wants everything</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-28</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>3:33</v>
+        <v>2:45</v>
       </c>
       <c r="H153" t="str">
-        <v>Isaia Huron</v>
+        <v>BIA</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L153" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-28</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G154" t="str">
-        <v>3:44</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Slayyyter</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L154" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Kingdom of Fear</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-28</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Deep Water - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G155" t="str">
-        <v>2:41</v>
+        <v>3:44</v>
       </c>
       <c r="H155" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L155" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>R3verse</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-28</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>takeaways</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G156" t="str">
-        <v>3:31</v>
+        <v>2:41</v>
       </c>
       <c r="H156" t="str">
-        <v>Medium Build</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L156" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>R3verse</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-28</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>takeaways</v>
       </c>
       <c r="G157" t="str">
-        <v>2:32</v>
+        <v>3:31</v>
       </c>
       <c r="H157" t="str">
-        <v>MIKE</v>
+        <v>Medium Build</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L157" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>heart of gold</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-28</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>heart of gold - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G158" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H158" t="str">
-        <v>kai devega</v>
+        <v>MIKE</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L158" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Breaking Down</v>
+        <v>heart of gold</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-28</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Skeletor</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:21</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Chief Keef</v>
+        <v>kai devega</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L159" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Dream House</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-28</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Dream House - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G160" t="str">
-        <v>2:54</v>
+        <v>4:21</v>
       </c>
       <c r="H160" t="str">
-        <v>Empress Of</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L160" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Baby Blue</v>
+        <v>Dream House</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-28</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H161" t="str">
-        <v>Cody Simpson</v>
+        <v>Empress Of</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L161" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-28</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:37</v>
+        <v>2:51</v>
       </c>
       <c r="H162" t="str">
-        <v>MEDUZA</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L162" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-28</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Forever Now</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:05</v>
+        <v>2:37</v>
       </c>
       <c r="H163" t="str">
-        <v>Switchfoot</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L163" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-28</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Forever Now</v>
       </c>
       <c r="G164" t="str">
-        <v>3:46</v>
+        <v>4:05</v>
       </c>
       <c r="H164" t="str">
-        <v>Benny G</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L164" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Cry In Front Of You</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-28</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>3:03</v>
+        <v>3:46</v>
       </c>
       <c r="H165" t="str">
-        <v>Eric Bellinger</v>
+        <v>Benny G</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L165" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-28</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:19</v>
+        <v>3:03</v>
       </c>
       <c r="H166" t="str">
-        <v>Anish Kumar</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L166" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>GASLIGHT</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-28</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:10</v>
+        <v>4:19</v>
       </c>
       <c r="H167" t="str">
-        <v>WesGhost</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L167" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Truth To Be Told</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-28</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:17</v>
+        <v>2:10</v>
       </c>
       <c r="H168" t="str">
-        <v>GERD</v>
+        <v>WesGhost</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L168" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Free Your Mind</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-28</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Prospa</v>
+        <v>GERD</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L169" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Down To The Bone</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-28</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H170" t="str">
-        <v>Josh Baker</v>
+        <v>Prospa</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L170" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Breathe</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-28</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Breathe - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:48</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L171" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>xs</v>
+        <v>Breathe</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-28</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>xs - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:19</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>Ashley Cooke</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L172" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Sail</v>
+        <v>xs</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-28</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>xs - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>4:54</v>
+        <v>3:19</v>
       </c>
       <c r="H173" t="str">
-        <v>Future Islands</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L173" t="str">
-        <v>Sail - Future Islands</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Dreaming</v>
+        <v>Sail</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-28</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Dear Nashville</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G174" t="str">
-        <v>3:33</v>
+        <v>4:54</v>
       </c>
       <c r="H174" t="str">
-        <v>Ashley Monroe</v>
+        <v>Future Islands</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L174" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>NEW TINGZ</v>
+        <v>Dreaming</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-28</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G175" t="str">
-        <v>2:39</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Armanii</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L175" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>La Opinión</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-28</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Mis Compas El Final</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>2:39</v>
       </c>
       <c r="H176" t="str">
-        <v>Joss Favela</v>
+        <v>Armanii</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L176" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>qué ves en mí?</v>
+        <v>La Opinión</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-28</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G177" t="str">
-        <v>3:24</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>Paloma Morphy</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L177" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-28</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:43</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L178" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>TUTUTU</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-28</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:16</v>
+        <v>2:43</v>
       </c>
       <c r="H179" t="str">
-        <v>ELENA ROSE</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L179" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-28</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:56</v>
+        <v>2:16</v>
       </c>
       <c r="H180" t="str">
-        <v>2'Live Bre</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L180" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Me Neither</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-28</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Heavy On The Soul</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:32</v>
+        <v>2:56</v>
       </c>
       <c r="H181" t="str">
-        <v>Ty Myers</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L181" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cole Palmer</v>
+        <v>Me Neither</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-28</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Solid Ground</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G182" t="str">
-        <v>2:48</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Limoblaze</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L182" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Wonder</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-28</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Wonder - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G183" t="str">
-        <v>3:48</v>
+        <v>2:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Meeks Carter</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L183" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>ICU</v>
+        <v>Wonder</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-28</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>ICU - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:53</v>
+        <v>3:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L184" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>ICU</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-28</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:45</v>
+        <v>2:53</v>
       </c>
       <c r="H185" t="str">
-        <v>Jozzy</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L185" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Waiting Room</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-28</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Waiting Room - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G186" t="str">
-        <v>3:21</v>
+        <v>2:45</v>
       </c>
       <c r="H186" t="str">
-        <v>Jenevieve</v>
+        <v>Jozzy</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L186" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-28</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Rise</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:02</v>
+        <v>3:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L187" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Roll On Thru</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-28</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G188" t="str">
-        <v>3:51</v>
+        <v>4:02</v>
       </c>
       <c r="H188" t="str">
-        <v>Hayden Everett</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L188" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Delicately</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-28</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Delicately - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:20</v>
+        <v>3:51</v>
       </c>
       <c r="H189" t="str">
-        <v>Andrea Bejar</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L189" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>One Of Those Things</v>
+        <v>Delicately</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-28</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L190" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>For Every Dusk</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-28</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>6:04</v>
+        <v>3:27</v>
       </c>
       <c r="H191" t="str">
-        <v>José González</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L191" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I'll Wait</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-28</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G192" t="str">
-        <v>3:33</v>
+        <v>6:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Buzzy Lee</v>
+        <v>José González</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L192" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Daisy</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-28</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Daisy - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G193" t="str">
-        <v>3:02</v>
+        <v>3:33</v>
       </c>
       <c r="H193" t="str">
-        <v>Lola Blue</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L193" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Daisy</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-28</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Friend Remixes</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H194" t="str">
-        <v>james K</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L194" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-28</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Perdidos - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G195" t="str">
-        <v>2:45</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>MAVICA</v>
+        <v>james K</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L195" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Fort</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-28</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Fort - Single</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:27</v>
+        <v>2:45</v>
       </c>
       <c r="H196" t="str">
-        <v>Lamb</v>
+        <v>MAVICA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L196" t="str">
-        <v>Fort - Lamb</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SAME LA</v>
+        <v>Fort</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-28</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>SAME LA - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:44</v>
+        <v>2:27</v>
       </c>
       <c r="H197" t="str">
-        <v>Tiffany Day</v>
+        <v>Lamb</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L197" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Working On It</v>
+        <v>SAME LA</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-28</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Working On It - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:06</v>
+        <v>3:44</v>
       </c>
       <c r="H198" t="str">
-        <v>Arthur Hill</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L198" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>spring cleaning</v>
+        <v>Working On It</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-28</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:03</v>
+        <v>3:06</v>
       </c>
       <c r="H199" t="str">
-        <v>Ethan Regan</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L199" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Just Drivin'</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-28</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H200" t="str">
-        <v>Presley Haile</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L200" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Simple Things</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-28</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Simple Things - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:46</v>
+        <v>3:26</v>
       </c>
       <c r="H201" t="str">
-        <v>Evening Elephants</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L201" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Want It Back</v>
+        <v>Simple Things</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-28</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Want It Back - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:27</v>
+        <v>3:46</v>
       </c>
       <c r="H202" t="str">
-        <v>Giant Rooks</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L202" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Bite Down</v>
+        <v>Want It Back</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-28</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Bite Down - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:36</v>
+        <v>3:27</v>
       </c>
       <c r="H203" t="str">
-        <v>Anna Sofia</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L203" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Bite Down</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-28</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>5:42</v>
+        <v>3:36</v>
       </c>
       <c r="H204" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L204" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Demons</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-28</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G205" t="str">
-        <v>2:42</v>
+        <v>5:42</v>
       </c>
       <c r="H205" t="str">
-        <v>Anella</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L205" t="str">
-        <v>Demons - Anella</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Es brennt...</v>
+        <v>Demons</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-28</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G206" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H206" t="str">
-        <v>Till Lindemann</v>
+        <v>Anella</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L206" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Fire Marengo</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-28</v>
@@ -8241,68 +8241,106 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:49</v>
+        <v>3:35</v>
       </c>
       <c r="H207" t="str">
-        <v>Enslaved</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L207" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D208" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
+      <c r="D209" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G208" t="str">
+      <c r="G209" t="str">
         <v>4:09</v>
       </c>
-      <c r="H208" t="str">
+      <c r="H209" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K208" t="str">
+      <c r="K209" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L208" t="str">
+      <c r="L209" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>